--- a/MacLarnon__1996/MacLarnon__1996_Table1_snapshot.xlsx
+++ b/MacLarnon__1996/MacLarnon__1996_Table1_snapshot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://computingservices-my.sharepoint.com/personal/mg2544_bath_ac_uk/Documents/Research Schemes/Allen Institue/Evo-M1-Trait-Data/MacLarnon__1996_Table1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/MacLarnon__1996/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC1048E3599F62A65ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C224EF5-197B-4027-8EED-BB66EDE0620C}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_F25DC773A252ABDACC1048E3599F62A65ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAA425AE-151F-5E47-944B-196E88D2FF96}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23880" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -518,7 +518,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="204"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -649,44 +649,44 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -973,19 +973,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.08984375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.08984375" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="16.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1007,10 +1007,10 @@
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -1020,10 +1020,10 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:9" ht="42" x14ac:dyDescent="0.35">
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>14</v>
       </c>
@@ -1045,10 +1045,10 @@
       <c r="G3" s="13">
         <v>11</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+    </row>
+    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>19</v>
       </c>
@@ -1070,10 +1070,10 @@
       <c r="G4" s="13">
         <v>11</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+    </row>
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>21</v>
       </c>
@@ -1095,10 +1095,10 @@
       <c r="G5" s="13">
         <v>1</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>26</v>
       </c>
@@ -1120,10 +1120,10 @@
       <c r="G6" s="13">
         <v>2</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>31</v>
       </c>
@@ -1145,10 +1145,10 @@
       <c r="G7" s="13">
         <v>1</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>34</v>
       </c>
@@ -1170,10 +1170,10 @@
       <c r="G8" s="13">
         <v>1</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>37</v>
       </c>
@@ -1195,10 +1195,10 @@
       <c r="G9" s="13">
         <v>1</v>
       </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+    </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>41</v>
       </c>
@@ -1220,10 +1220,10 @@
       <c r="G10" s="13">
         <v>1</v>
       </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>44</v>
       </c>
@@ -1245,10 +1245,10 @@
       <c r="G11" s="13">
         <v>1</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>47</v>
       </c>
@@ -1270,10 +1270,10 @@
       <c r="G12" s="13">
         <v>1</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>50</v>
       </c>
@@ -1295,10 +1295,10 @@
       <c r="G13" s="13">
         <v>3</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>50</v>
       </c>
@@ -1320,10 +1320,10 @@
       <c r="G14" s="13">
         <v>3</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+    </row>
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>54</v>
       </c>
@@ -1345,10 +1345,10 @@
       <c r="G15" s="13">
         <v>1</v>
       </c>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-    </row>
-    <row r="16" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+    </row>
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>57</v>
       </c>
@@ -1370,10 +1370,10 @@
       <c r="G16" s="13">
         <v>2</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>61</v>
       </c>
@@ -1395,10 +1395,10 @@
       <c r="G17" s="13">
         <v>2</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>66</v>
       </c>
@@ -1420,10 +1420,10 @@
       <c r="G18" s="13">
         <v>3</v>
       </c>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>66</v>
       </c>
@@ -1445,10 +1445,10 @@
       <c r="G19" s="13">
         <v>3</v>
       </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+    </row>
+    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>71</v>
       </c>
@@ -1470,10 +1470,10 @@
       <c r="G20" s="13">
         <v>3</v>
       </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+    </row>
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>71</v>
       </c>
@@ -1495,10 +1495,10 @@
       <c r="G21" s="13">
         <v>3</v>
       </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>5</v>
       </c>
@@ -1520,10 +1520,10 @@
       <c r="G22" s="13">
         <v>1</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+    </row>
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="21" t="s">
         <v>4</v>
       </c>
@@ -1539,16 +1539,16 @@
       <c r="E23" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="23" t="s">
         <v>124</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
         <v>3</v>
       </c>
@@ -1558,10 +1558,10 @@
       <c r="E24" s="20"/>
       <c r="F24" s="22"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-    </row>
-    <row r="25" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>86</v>
       </c>
@@ -1583,10 +1583,10 @@
       <c r="G25" s="13">
         <v>5</v>
       </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+    </row>
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>86</v>
       </c>
@@ -1608,10 +1608,10 @@
       <c r="G26" s="13">
         <v>5</v>
       </c>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+    </row>
+    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>93</v>
       </c>
@@ -1633,10 +1633,10 @@
       <c r="G27" s="13">
         <v>5</v>
       </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+    </row>
+    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>97</v>
       </c>
@@ -1658,10 +1658,10 @@
       <c r="G28" s="13">
         <v>5</v>
       </c>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+    </row>
+    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>97</v>
       </c>
@@ -1683,23 +1683,23 @@
       <c r="G29" s="13">
         <v>5</v>
       </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="24" t="s">
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B30" s="14"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
         <v>105</v>
       </c>
@@ -1712,7 +1712,7 @@
       <c r="D31" s="17">
         <v>85</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="25">
         <v>430</v>
       </c>
       <c r="F31" s="10" t="s">
@@ -1721,11 +1721,11 @@
       <c r="G31" s="13">
         <v>4</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="1:9" ht="56" x14ac:dyDescent="0.35">
-      <c r="A32" s="28" t="s">
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+    </row>
+    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A32" s="26" t="s">
         <v>107</v>
       </c>
       <c r="B32" s="10" t="s">
@@ -1746,11 +1746,11 @@
       <c r="G32" s="13">
         <v>4</v>
       </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-    </row>
-    <row r="33" spans="1:9" ht="56" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+    </row>
+    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A33" s="26" t="s">
         <v>107</v>
       </c>
       <c r="B33" s="10" t="s">
@@ -1771,11 +1771,11 @@
       <c r="G33" s="13">
         <v>4</v>
       </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-    </row>
-    <row r="34" spans="1:9" ht="56" x14ac:dyDescent="0.35">
-      <c r="A34" s="28" t="s">
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+    </row>
+    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A34" s="26" t="s">
         <v>109</v>
       </c>
       <c r="B34" s="10" t="s">
@@ -1796,11 +1796,11 @@
       <c r="G34" s="13">
         <v>6</v>
       </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" spans="1:9" ht="56" x14ac:dyDescent="0.35">
-      <c r="A35" s="28" t="s">
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+    </row>
+    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A35" s="26" t="s">
         <v>109</v>
       </c>
       <c r="B35" s="10" t="s">
@@ -1821,10 +1821,10 @@
       <c r="G35" s="13">
         <v>6</v>
       </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="21" t="s">
         <v>6</v>
       </c>
@@ -1846,10 +1846,10 @@
       <c r="G36" s="13">
         <v>7</v>
       </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="21" t="s">
         <v>7</v>
       </c>
@@ -1857,13 +1857,13 @@
       <c r="C37" s="11"/>
       <c r="D37" s="15"/>
       <c r="E37" s="17"/>
-      <c r="F37" s="29"/>
+      <c r="F37" s="27"/>
       <c r="G37" s="13"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-    </row>
-    <row r="38" spans="1:9" ht="42" x14ac:dyDescent="0.35">
-      <c r="A38" s="30" t="s">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="A38" s="28" t="s">
         <v>111</v>
       </c>
       <c r="B38" s="10" t="s">
@@ -1884,11 +1884,11 @@
       <c r="G38" s="13">
         <v>8</v>
       </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-    </row>
-    <row r="39" spans="1:9" ht="42" x14ac:dyDescent="0.35">
-      <c r="A39" s="30" t="s">
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+    </row>
+    <row r="39" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="A39" s="28" t="s">
         <v>111</v>
       </c>
       <c r="B39" s="10" t="s">
@@ -1909,11 +1909,11 @@
       <c r="G39" s="13">
         <v>8</v>
       </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-    </row>
-    <row r="40" spans="1:9" ht="42" x14ac:dyDescent="0.35">
-      <c r="A40" s="30" t="s">
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+    </row>
+    <row r="40" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="A40" s="28" t="s">
         <v>112</v>
       </c>
       <c r="B40" s="10" t="s">
@@ -1934,11 +1934,11 @@
       <c r="G40" s="13">
         <v>9</v>
       </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-    </row>
-    <row r="41" spans="1:9" ht="42" x14ac:dyDescent="0.35">
-      <c r="A41" s="30" t="s">
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+    </row>
+    <row r="41" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="A41" s="28" t="s">
         <v>112</v>
       </c>
       <c r="B41" s="10" t="s">
@@ -1959,23 +1959,23 @@
       <c r="G41" s="13">
         <v>9</v>
       </c>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A42" s="24" t="s">
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-    </row>
-    <row r="43" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="B42" s="14"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+    </row>
+    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
         <v>116</v>
       </c>
@@ -1997,10 +1997,10 @@
       <c r="G43" s="13">
         <v>4</v>
       </c>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-    </row>
-    <row r="44" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
         <v>117</v>
       </c>
@@ -2022,10 +2022,10 @@
       <c r="G44" s="13">
         <v>4</v>
       </c>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
         <v>118</v>
       </c>
@@ -2038,7 +2038,7 @@
       <c r="D45" s="17">
         <v>80</v>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="25">
         <v>535</v>
       </c>
       <c r="F45" s="10" t="s">
@@ -2047,10 +2047,10 @@
       <c r="G45" s="13">
         <v>4</v>
       </c>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>118</v>
       </c>
@@ -2063,7 +2063,7 @@
       <c r="D46" s="17">
         <v>75</v>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="25">
         <v>492</v>
       </c>
       <c r="F46" s="10" t="s">
@@ -2072,10 +2072,10 @@
       <c r="G46" s="13">
         <v>4</v>
       </c>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-    </row>
-    <row r="47" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+    </row>
+    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>119</v>
       </c>
@@ -2097,10 +2097,10 @@
       <c r="G47" s="13">
         <v>4</v>
       </c>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-    </row>
-    <row r="48" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+    </row>
+    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
         <v>119</v>
       </c>
@@ -2122,10 +2122,10 @@
       <c r="G48" s="13">
         <v>4</v>
       </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-    </row>
-    <row r="49" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
         <v>120</v>
       </c>
@@ -2147,10 +2147,10 @@
       <c r="G49" s="13">
         <v>4</v>
       </c>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-    </row>
-    <row r="50" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="H49" s="35"/>
+      <c r="I49" s="35"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
         <v>120</v>
       </c>
@@ -2172,48 +2172,48 @@
       <c r="G50" s="13">
         <v>4</v>
       </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A51" s="24" t="s">
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B51" s="25"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A52" s="31" t="s">
+      <c r="B51" s="14"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="35"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" s="29" t="s">
         <v>122</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="30">
         <v>48</v>
       </c>
-      <c r="D52" s="33">
+      <c r="D52" s="31">
         <v>54</v>
       </c>
-      <c r="E52" s="34">
+      <c r="E52" s="32">
         <v>117</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G52" s="35">
+      <c r="G52" s="33">
         <v>4</v>
       </c>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="1:9" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+    </row>
+    <row r="53" spans="1:9" ht="113" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="36" t="s">
         <v>123</v>
       </c>
@@ -2228,65 +2228,74 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
     <mergeCell ref="H48:I48"/>
     <mergeCell ref="H49:I49"/>
     <mergeCell ref="H52:I52"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="H50:I50"/>
     <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -2539,19 +2548,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9605DCBE-15F4-4273-B047-8A9E2BA89D60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A78D33CC-51F3-4D96-9C4C-7ED5A1EB17F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A78D33CC-51F3-4D96-9C4C-7ED5A1EB17F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{365E451A-B6A8-4589-9422-EE2036FB4A82}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B75121B-A812-43E9-B110-0489C2C9F66C}"/>
 </file>